--- a/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>STEL</t>
   </si>
@@ -656,118 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>152200</v>
+      </c>
+      <c r="E8" s="3">
         <v>151300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>147000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>140400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>132000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>67900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>62800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>60300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>32100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -807,8 +813,11 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +857,11 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,8 +963,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -988,34 +1007,37 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E15" s="3">
         <v>-8800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>-8700</v>
       </c>
       <c r="F15" s="3">
         <v>-8700</v>
       </c>
       <c r="G15" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="H15" s="3">
         <v>-9000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>-1900</v>
       </c>
       <c r="I15" s="3">
         <v>-1900</v>
       </c>
       <c r="J15" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="K15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>-1100</v>
       </c>
       <c r="L15" s="3">
         <v>-1100</v>
@@ -1029,8 +1051,11 @@
       <c r="O15" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E17" s="3">
         <v>46900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>40600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>28300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>61100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-3400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-3600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E18" s="3">
         <v>104400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>106400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>112100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>70900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>58700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>55300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>53400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>31900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>35900</v>
       </c>
       <c r="M18" s="3">
         <v>35900</v>
       </c>
       <c r="N18" s="3">
-        <v>32500</v>
+        <v>35900</v>
       </c>
       <c r="O18" s="3">
         <v>32500</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,90 +1174,97 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-71100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-66100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-63800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-65100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-69000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-41100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-35200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-30500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-30600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-18600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-21500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-20000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-19900</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E21" s="3">
         <v>47200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>51400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>55800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>10800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>19400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>21900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>24600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>18400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>15400</v>
-      </c>
-      <c r="N21" s="3">
-        <v>13600</v>
       </c>
       <c r="O21" s="3">
         <v>13600</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1265,90 +1304,99 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E23" s="3">
         <v>38400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>42600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>47100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>20100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>17300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14400</v>
-      </c>
-      <c r="N23" s="3">
-        <v>12500</v>
       </c>
       <c r="O23" s="3">
         <v>12500</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E24" s="3">
         <v>7400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E26" s="3">
         <v>30900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>35200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>37100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>18700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>11700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E27" s="3">
         <v>30900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>35200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>37100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,90 +1700,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E32" s="3">
         <v>66100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>63800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>65100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>69000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>41100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>35200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>30500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>30600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>18600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>21500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>20000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E33" s="3">
         <v>30900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>35200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>37100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>18700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E35" s="3">
         <v>30900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>35200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>37100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>18700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,90 +1963,97 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E41" s="3">
         <v>95000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>105900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>99200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>67100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>41200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>42000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>47700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>27700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>50600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>49700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>52500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>303300</v>
+      </c>
+      <c r="E42" s="3">
         <v>236300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>222700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>183800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>319700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>347100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>460100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>740400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>940200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>965500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>755500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>571000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>509800</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2001,8 +2093,11 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2042,8 +2137,11 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2083,8 +2181,11 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2124,8 +2225,11 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2165,90 +2269,99 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>118700</v>
+      </c>
+      <c r="E48" s="3">
         <v>119300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>119100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>124700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>126800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>66600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>67300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>67500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>69600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>70800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>72500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>73500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>74400</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>614000</v>
+      </c>
+      <c r="E49" s="3">
         <v>620300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>627100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>633900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>640800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>84100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>84300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>84500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>84600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>84700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>84800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>84900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,8 +2445,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2346,32 +2465,35 @@
       <c r="G52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3">
         <v>29600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>9800</v>
       </c>
       <c r="M52" s="3">
         <v>9800</v>
       </c>
       <c r="N52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="O52" s="3">
         <v>11000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10647100</v>
+      </c>
+      <c r="E54" s="3">
         <v>10665500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10778400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10604700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10900400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4271800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4322300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4446000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4486000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4209100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4066500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4028600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3949200</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,26 +2615,27 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E57" s="3">
         <v>7600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>5</v>
       </c>
@@ -2518,8 +2648,8 @@
       <c r="L57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -2527,8 +2657,11 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2568,49 +2701,55 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E59" s="3">
         <v>20200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2650,26 +2789,29 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>159800</v>
+      </c>
+      <c r="E61" s="3">
         <v>433600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>479500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>348400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>173300</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2691,8 +2833,11 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2732,8 +2877,11 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9126100</v>
+      </c>
+      <c r="E66" s="3">
         <v>9204600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9319700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9158500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9517300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3770400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3795600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3906300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3923900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3644500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3510300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3483300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3402800</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>405900</v>
+      </c>
+      <c r="E72" s="3">
         <v>385600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>361600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>333400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>303100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>262800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>253200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>244700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>237200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>241000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>229800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>221300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>214500</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1521000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1460800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1458700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1446200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1383200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>501400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>526700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>539700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>562100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>564600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>556200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>545300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>546500</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E81" s="3">
         <v>30900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>35200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>37100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>18700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,37 +3624,38 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E83" s="3">
         <v>8800</v>
-      </c>
-      <c r="E83" s="3">
-        <v>8700</v>
       </c>
       <c r="F83" s="3">
         <v>8700</v>
       </c>
       <c r="G83" s="3">
+        <v>8700</v>
+      </c>
+      <c r="H83" s="3">
         <v>8400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1900</v>
       </c>
       <c r="I83" s="3">
         <v>1900</v>
       </c>
       <c r="J83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K83" s="3">
         <v>2000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>1100</v>
       </c>
       <c r="M83" s="3">
         <v>1100</v>
@@ -3468,8 +3666,11 @@
       <c r="O83" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E89" s="3">
         <v>38900</v>
-      </c>
-      <c r="E89" s="3">
-        <v>49000</v>
       </c>
       <c r="F89" s="3">
         <v>49000</v>
       </c>
       <c r="G89" s="3">
+        <v>49000</v>
+      </c>
+      <c r="H89" s="3">
         <v>34900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>33300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>16100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-20200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>30500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>15900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,40 +3950,41 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-1200</v>
       </c>
       <c r="F91" s="3">
         <v>-1200</v>
       </c>
       <c r="G91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H91" s="3">
         <v>-3100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-200</v>
       </c>
       <c r="J91" s="3">
         <v>-200</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-300</v>
       </c>
       <c r="N91" s="3">
         <v>-300</v>
@@ -3772,8 +3992,11 @@
       <c r="O91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>160500</v>
+      </c>
+      <c r="E94" s="3">
         <v>91600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-159900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>203000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>511100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-203200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-61900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-172300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-324600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>69000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>146300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-24700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,8 +4144,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3930,16 +4163,16 @@
         <v>-6900</v>
       </c>
       <c r="H96" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="I96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-2900</v>
       </c>
       <c r="J96" s="3">
         <v>-2900</v>
       </c>
       <c r="K96" s="3">
-        <v>-3200</v>
+        <v>-2900</v>
       </c>
       <c r="L96" s="3">
         <v>-3200</v>
@@ -3948,13 +4181,16 @@
         <v>-3200</v>
       </c>
       <c r="N96" s="3">
-        <v>-2500</v>
+        <v>-3200</v>
       </c>
       <c r="O96" s="3">
         <v>-2500</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>-2500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,49 +4318,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-94900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-132300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>151700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-360400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-386500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-48400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-246100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>112400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>296200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>110800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>28800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>75400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>123600</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4158,45 +4406,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>40800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-108400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>193900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-115000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-406500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-58100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-48600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>210400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>183700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>66700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>160400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>STEL</t>
   </si>
@@ -656,124 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>148400</v>
+      </c>
+      <c r="E8" s="3">
         <v>152200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>151300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>147000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>140400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>132000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>67900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>62800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>60300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>32300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -816,8 +823,11 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -860,8 +870,11 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +891,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +936,11 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +983,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1010,8 +1030,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1019,28 +1042,28 @@
         <v>-8200</v>
       </c>
       <c r="E15" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="F15" s="3">
         <v>-8800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>-8700</v>
       </c>
       <c r="G15" s="3">
         <v>-8700</v>
       </c>
       <c r="H15" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="I15" s="3">
         <v>-9000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>-1900</v>
       </c>
       <c r="J15" s="3">
         <v>-1900</v>
       </c>
       <c r="K15" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="L15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>-1100</v>
       </c>
       <c r="M15" s="3">
         <v>-1100</v>
@@ -1054,8 +1077,11 @@
       <c r="P15" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1095,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E17" s="3">
         <v>47300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>46900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>40600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>28300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>61100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-3400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-3600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E18" s="3">
         <v>104900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>104400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>106400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>112100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>70900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>58700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>55300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>53400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>31900</v>
-      </c>
-      <c r="M18" s="3">
-        <v>35900</v>
       </c>
       <c r="N18" s="3">
         <v>35900</v>
       </c>
       <c r="O18" s="3">
-        <v>32500</v>
+        <v>35900</v>
       </c>
       <c r="P18" s="3">
         <v>32500</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,96 +1208,103 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-65100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-71100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-66100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-63800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-65100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-69000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-41100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-35200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-30500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-30600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-18600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-21500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-20000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-19900</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E21" s="3">
         <v>42000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>47200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>51400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>55800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>21900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>24600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>18400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15400</v>
-      </c>
-      <c r="O21" s="3">
-        <v>13600</v>
       </c>
       <c r="P21" s="3">
         <v>13600</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,96 +1347,105 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E23" s="3">
         <v>33800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>38400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>42600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>47100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>22900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>17300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14400</v>
-      </c>
-      <c r="O23" s="3">
-        <v>12500</v>
       </c>
       <c r="P23" s="3">
         <v>12500</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E24" s="3">
         <v>6600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E26" s="3">
         <v>27300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>30900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>35200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>37100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E27" s="3">
         <v>27300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>30900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>35200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>37100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>14300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1770,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E32" s="3">
         <v>71100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>66100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>63800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>65100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>69000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>41100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>35200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>30500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>30600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>18600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>21500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>20000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E33" s="3">
         <v>27300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>30900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>35200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>37100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>14300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E35" s="3">
         <v>27300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>30900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>35200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>37100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>14300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,96 +2050,103 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E41" s="3">
         <v>121000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>95000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>105900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>99200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>67100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>41200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>42000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>47700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>27700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>50600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>49700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>52500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>341100</v>
+      </c>
+      <c r="E42" s="3">
         <v>303300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>236300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>222700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>183800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>319700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>347100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>460100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>740400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>940200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>965500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>755500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>571000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>509800</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2096,8 +2189,11 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2140,8 +2236,11 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2184,8 +2283,11 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2228,8 +2330,11 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2272,96 +2377,105 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>115700</v>
+      </c>
+      <c r="E48" s="3">
         <v>118700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>119300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>119100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>124700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>126800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>66600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>67300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>67500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>69600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>70800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>72500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>73500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>74400</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>607800</v>
+      </c>
+      <c r="E49" s="3">
         <v>614000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>620300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>627100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>633900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>640800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>84100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>84300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>84500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>84600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>84700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>84800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>84900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,8 +2565,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2468,32 +2588,35 @@
       <c r="H52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3">
         <v>29600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>9800</v>
       </c>
       <c r="N52" s="3">
         <v>9800</v>
       </c>
       <c r="O52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="P52" s="3">
         <v>11000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2659,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10729200</v>
+      </c>
+      <c r="E54" s="3">
         <v>10647100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10665500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10778400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10604700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10900400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4271800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4322300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4446000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4486000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4209100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4066500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4028600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3949200</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,29 +2746,30 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E57" s="3">
         <v>11300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2100</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
@@ -2651,8 +2782,8 @@
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
+      <c r="N57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
@@ -2660,8 +2791,11 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2704,52 +2838,58 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E59" s="3">
         <v>20700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>23100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2792,29 +2932,32 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>324900</v>
+      </c>
+      <c r="E61" s="3">
         <v>159800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>433600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>479500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>348400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>173300</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2836,8 +2979,11 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2880,8 +3026,11 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3167,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9198500</v>
+      </c>
+      <c r="E66" s="3">
         <v>9126100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9204600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9319700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9158500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9517300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3770400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3795600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3906300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3923900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3644500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3510300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3483300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3402800</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3421,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>425100</v>
+      </c>
+      <c r="E72" s="3">
         <v>405900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>385600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>361600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>333400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>303100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>262800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>253200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>244700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>237200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>241000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>229800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>221300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>214500</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3609,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1530700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1521000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1460800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1458700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1446200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1383200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>501400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>526700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>539700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>562100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>564600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>556200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>545300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>546500</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E81" s="3">
         <v>27300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>30900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>35200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>37100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>14300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +3823,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3634,31 +3833,31 @@
         <v>8200</v>
       </c>
       <c r="E83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F83" s="3">
         <v>8800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>8700</v>
       </c>
       <c r="G83" s="3">
         <v>8700</v>
       </c>
       <c r="H83" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I83" s="3">
         <v>8400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1900</v>
       </c>
       <c r="J83" s="3">
         <v>1900</v>
       </c>
       <c r="K83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L83" s="3">
         <v>2000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>1100</v>
       </c>
       <c r="N83" s="3">
         <v>1100</v>
@@ -3669,8 +3868,11 @@
       <c r="P83" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E89" s="3">
         <v>31300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38900</v>
-      </c>
-      <c r="F89" s="3">
-        <v>49000</v>
       </c>
       <c r="G89" s="3">
         <v>49000</v>
       </c>
       <c r="H89" s="3">
+        <v>49000</v>
+      </c>
+      <c r="I89" s="3">
         <v>34900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>33300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>16100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-20200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>30500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>15900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,43 +4171,44 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-1200</v>
       </c>
       <c r="G91" s="3">
         <v>-1200</v>
       </c>
       <c r="H91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I91" s="3">
         <v>-3100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-200</v>
       </c>
       <c r="K91" s="3">
         <v>-200</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-300</v>
       </c>
       <c r="O91" s="3">
         <v>-300</v>
@@ -3995,8 +4216,11 @@
       <c r="P91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4310,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-109600</v>
+      </c>
+      <c r="E94" s="3">
         <v>160500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>91600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-159900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>203000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>511100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-203200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-61900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-172300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-324600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>69000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>146300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-24700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,13 +4378,14 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-6900</v>
+        <v>-7000</v>
       </c>
       <c r="E96" s="3">
         <v>-6900</v>
@@ -4166,16 +4400,16 @@
         <v>-6900</v>
       </c>
       <c r="I96" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="J96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-2900</v>
       </c>
       <c r="K96" s="3">
         <v>-2900</v>
       </c>
       <c r="L96" s="3">
-        <v>-3200</v>
+        <v>-2900</v>
       </c>
       <c r="M96" s="3">
         <v>-3200</v>
@@ -4184,13 +4418,16 @@
         <v>-3200</v>
       </c>
       <c r="O96" s="3">
-        <v>-2500</v>
+        <v>-3200</v>
       </c>
       <c r="P96" s="3">
         <v>-2500</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>-2500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4564,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-94900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-132300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>151700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-360400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-386500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-48400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-246100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>112400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>296200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>110800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>28800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>75400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>123600</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4409,48 +4658,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>500</v>
+      </c>
+      <c r="E102" s="3">
         <v>97000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>40800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-108400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>193900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-115000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-406500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-58100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-48600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>210400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>183700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>66700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>160400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>STEL</t>
   </si>
@@ -656,131 +656,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>152200</v>
+      </c>
+      <c r="E8" s="3">
         <v>148400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>152200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>151300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>147000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>140400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>132000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>67900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>62800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>60300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>32500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -826,8 +833,11 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +905,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -939,8 +953,11 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1003,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1033,8 +1053,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1045,28 +1068,28 @@
         <v>-8200</v>
       </c>
       <c r="F15" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="G15" s="3">
         <v>-8800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>-8700</v>
       </c>
       <c r="H15" s="3">
         <v>-8700</v>
       </c>
       <c r="I15" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="J15" s="3">
         <v>-9000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>-1900</v>
       </c>
       <c r="K15" s="3">
         <v>-1900</v>
       </c>
       <c r="L15" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="M15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>-1100</v>
       </c>
       <c r="N15" s="3">
         <v>-1100</v>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1122,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E17" s="3">
         <v>50400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>47300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>46900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>40600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>28300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>61100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-3400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-3600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>103400</v>
+      </c>
+      <c r="E18" s="3">
         <v>98000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>104900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>104400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>106400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>112100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>70900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>58700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>55300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>53400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>31900</v>
-      </c>
-      <c r="N18" s="3">
-        <v>35900</v>
       </c>
       <c r="O18" s="3">
         <v>35900</v>
       </c>
       <c r="P18" s="3">
-        <v>32500</v>
+        <v>35900</v>
       </c>
       <c r="Q18" s="3">
         <v>32500</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,102 +1242,109 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-65800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-65100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-71100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-66100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-63800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-65100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-69000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-41100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-35200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-30500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-30600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-18600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-21500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-19900</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>45700</v>
+      </c>
+      <c r="E21" s="3">
         <v>41100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>42000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>47200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>51400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>55800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>21900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>24600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15400</v>
-      </c>
-      <c r="P21" s="3">
-        <v>13600</v>
       </c>
       <c r="Q21" s="3">
         <v>13600</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1350,102 +1390,111 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E23" s="3">
         <v>32900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>33800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>38400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>42600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>47100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>17700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>22900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>17300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14400</v>
-      </c>
-      <c r="P23" s="3">
-        <v>12500</v>
       </c>
       <c r="Q23" s="3">
         <v>12500</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E24" s="3">
         <v>6800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E26" s="3">
         <v>26100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>27300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>30900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>35200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>37100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>14300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>18700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>11700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E27" s="3">
         <v>26100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>27300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>30900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>35200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>37100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>14300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>18700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,102 +1840,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E32" s="3">
         <v>65100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>71100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>66100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>63800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>65100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>69000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>41100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>35200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>30500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>30600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>18600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>21500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>20000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E33" s="3">
         <v>26100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>27300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>30900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>35200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>37100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>14300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>18700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E35" s="3">
         <v>26100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>27300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>30900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>35200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>37100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>14300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>18700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,102 +2137,109 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>110300</v>
+      </c>
+      <c r="E41" s="3">
         <v>74700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>121000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>95000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>105900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>99200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>67100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>41200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>42000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>47700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>27700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>50600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>49700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>52500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>395000</v>
+      </c>
+      <c r="E42" s="3">
         <v>341100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>303300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>236300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>222700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>183800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>319700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>347100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>460100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>740400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>940200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>965500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>755500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>571000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>509800</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2192,8 +2285,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2239,8 +2335,11 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2286,8 +2385,11 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2333,8 +2435,11 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2380,102 +2485,111 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E48" s="3">
         <v>115700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>118700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>119300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>119100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>124700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>126800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>66600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>67300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>67500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>69600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>70800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>72500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>73500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>74400</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>601600</v>
+      </c>
+      <c r="E49" s="3">
         <v>607800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>614000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>620300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>627100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>633900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>640800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>84100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>84300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>84500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>84600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>84700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>84800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>84900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,8 +2685,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2591,32 +2711,35 @@
       <c r="I52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
         <v>29600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10000</v>
-      </c>
-      <c r="N52" s="3">
-        <v>9800</v>
       </c>
       <c r="O52" s="3">
         <v>9800</v>
       </c>
       <c r="P52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="Q52" s="3">
         <v>11000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2785,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10723700</v>
+      </c>
+      <c r="E54" s="3">
         <v>10729200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10647100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10665500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10778400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10604700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10900400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4271800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4322300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4446000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4486000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4209100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4066500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4028600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3949200</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,32 +2877,33 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E57" s="3">
         <v>12200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>5</v>
       </c>
@@ -2785,8 +2916,8 @@
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -2794,8 +2925,11 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2841,55 +2975,61 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E59" s="3">
         <v>19700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>23100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2935,32 +3075,35 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>350000</v>
+      </c>
+      <c r="E61" s="3">
         <v>324900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>159800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>433600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>479500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>348400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>173300</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2982,8 +3125,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3029,8 +3175,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3325,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9157900</v>
+      </c>
+      <c r="E66" s="3">
         <v>9198500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9126100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9204600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9319700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9158500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9517300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3770400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3795600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3906300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3923900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3644500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3510300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3483300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3402800</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3595,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>447900</v>
+      </c>
+      <c r="E72" s="3">
         <v>425100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>405900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>385600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>361600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>333400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>303100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>262800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>253200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>244700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>237200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>241000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>229800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>221300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>214500</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3795,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1565800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1530700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1521000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1460800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1458700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1446200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1383200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>501400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>526700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>539700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>562100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>564600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>556200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>545300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>546500</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E81" s="3">
         <v>26100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>27300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>30900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>35200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>37100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>14300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>18700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4022,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3836,31 +4035,31 @@
         <v>8200</v>
       </c>
       <c r="F83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="G83" s="3">
         <v>8800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>8700</v>
       </c>
       <c r="H83" s="3">
         <v>8700</v>
       </c>
       <c r="I83" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J83" s="3">
         <v>8400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1900</v>
       </c>
       <c r="K83" s="3">
         <v>1900</v>
       </c>
       <c r="L83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M83" s="3">
         <v>2000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>1100</v>
       </c>
       <c r="O83" s="3">
         <v>1100</v>
@@ -3871,8 +4070,11 @@
       <c r="Q83" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E89" s="3">
         <v>31100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>31300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38900</v>
-      </c>
-      <c r="G89" s="3">
-        <v>49000</v>
       </c>
       <c r="H89" s="3">
         <v>49000</v>
       </c>
       <c r="I89" s="3">
+        <v>49000</v>
+      </c>
+      <c r="J89" s="3">
         <v>34900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>33300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>24800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>16100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-20200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>30500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>15900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,46 +4392,47 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-1200</v>
       </c>
       <c r="H91" s="3">
         <v>-1200</v>
       </c>
       <c r="I91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J91" s="3">
         <v>-3100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-200</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-300</v>
       </c>
       <c r="P91" s="3">
         <v>-300</v>
@@ -4219,8 +4440,11 @@
       <c r="Q91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4540,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>103300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-109600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>160500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>91600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-159900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>203000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>511100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-203200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-61900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-172300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-324600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>69000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>146300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,16 +4612,17 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E96" s="3">
         <v>-7000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-6900</v>
       </c>
       <c r="F96" s="3">
         <v>-6900</v>
@@ -4403,16 +4637,16 @@
         <v>-6900</v>
       </c>
       <c r="J96" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="K96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-2900</v>
       </c>
       <c r="L96" s="3">
         <v>-2900</v>
       </c>
       <c r="M96" s="3">
-        <v>-3200</v>
+        <v>-2900</v>
       </c>
       <c r="N96" s="3">
         <v>-3200</v>
@@ -4421,13 +4655,16 @@
         <v>-3200</v>
       </c>
       <c r="P96" s="3">
-        <v>-2500</v>
+        <v>-3200</v>
       </c>
       <c r="Q96" s="3">
         <v>-2500</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>-2500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,55 +4810,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-50900</v>
+      </c>
+      <c r="E100" s="3">
         <v>79000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-94900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-132300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>151700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-360400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-386500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-48400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-246100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>112400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>296200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>110800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>28800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>75400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>123600</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4661,51 +4910,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>90500</v>
+      </c>
+      <c r="E102" s="3">
         <v>500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>97000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>40800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-108400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>193900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-115000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-406500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-58100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-48600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>210400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>183700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>66700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>160400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>STEL</t>
   </si>
@@ -656,138 +656,145 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>152200</v>
+        <v>113800</v>
       </c>
       <c r="E8" s="3">
-        <v>148400</v>
+        <v>108800</v>
       </c>
       <c r="F8" s="3">
-        <v>152200</v>
+        <v>104300</v>
       </c>
       <c r="G8" s="3">
-        <v>151300</v>
+        <v>111800</v>
       </c>
       <c r="H8" s="3">
-        <v>147000</v>
+        <v>109100</v>
       </c>
       <c r="I8" s="3">
-        <v>140400</v>
+        <v>111800</v>
       </c>
       <c r="J8" s="3">
+        <v>119700</v>
+      </c>
+      <c r="K8" s="3">
         <v>132000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>67900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>62800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>60300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>32100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>32300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -836,31 +843,34 @@
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>113800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>108800</v>
+      </c>
+      <c r="F10" s="3">
+        <v>104300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>111800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>109100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>111800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>119700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -886,8 +896,11 @@
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,8 +919,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -956,8 +970,11 @@
       <c r="R12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,31 +1023,34 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1056,43 +1076,46 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-8200</v>
+        <v>8100</v>
       </c>
       <c r="E15" s="3">
-        <v>-8200</v>
+        <v>8200</v>
       </c>
       <c r="F15" s="3">
-        <v>-8200</v>
+        <v>8200</v>
       </c>
       <c r="G15" s="3">
-        <v>-8800</v>
+        <v>8200</v>
       </c>
       <c r="H15" s="3">
-        <v>-8700</v>
+        <v>8800</v>
       </c>
       <c r="I15" s="3">
-        <v>-8700</v>
+        <v>8700</v>
       </c>
       <c r="J15" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K15" s="3">
         <v>-9000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>-1900</v>
       </c>
       <c r="L15" s="3">
         <v>-1900</v>
       </c>
       <c r="M15" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="N15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>-1100</v>
       </c>
       <c r="O15" s="3">
         <v>-1100</v>
@@ -1106,8 +1129,11 @@
       <c r="R15" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1149,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>48800</v>
+        <v>63100</v>
       </c>
       <c r="E17" s="3">
-        <v>50400</v>
+        <v>62700</v>
       </c>
       <c r="F17" s="3">
-        <v>47300</v>
+        <v>63300</v>
       </c>
       <c r="G17" s="3">
-        <v>46900</v>
+        <v>63500</v>
       </c>
       <c r="H17" s="3">
-        <v>40600</v>
+        <v>58600</v>
       </c>
       <c r="I17" s="3">
-        <v>28300</v>
+        <v>56700</v>
       </c>
       <c r="J17" s="3">
+        <v>58300</v>
+      </c>
+      <c r="K17" s="3">
         <v>61100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-3400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>103400</v>
+        <v>50700</v>
       </c>
       <c r="E18" s="3">
-        <v>98000</v>
+        <v>46100</v>
       </c>
       <c r="F18" s="3">
-        <v>104900</v>
+        <v>41000</v>
       </c>
       <c r="G18" s="3">
-        <v>104400</v>
+        <v>48300</v>
       </c>
       <c r="H18" s="3">
-        <v>106400</v>
+        <v>50500</v>
       </c>
       <c r="I18" s="3">
-        <v>112100</v>
+        <v>55200</v>
       </c>
       <c r="J18" s="3">
+        <v>61400</v>
+      </c>
+      <c r="K18" s="3">
         <v>70900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>58700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>55300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>53400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>31900</v>
-      </c>
-      <c r="O18" s="3">
-        <v>35900</v>
       </c>
       <c r="P18" s="3">
         <v>35900</v>
       </c>
       <c r="Q18" s="3">
-        <v>32500</v>
+        <v>35900</v>
       </c>
       <c r="R18" s="3">
         <v>32500</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,131 +1276,138 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-65800</v>
+        <v>8000</v>
       </c>
       <c r="E20" s="3">
-        <v>-65100</v>
+        <v>8500</v>
       </c>
       <c r="F20" s="3">
-        <v>-71100</v>
+        <v>8100</v>
       </c>
       <c r="G20" s="3">
-        <v>-66100</v>
+        <v>11400</v>
       </c>
       <c r="H20" s="3">
-        <v>-63800</v>
+        <v>8700</v>
       </c>
       <c r="I20" s="3">
-        <v>-65100</v>
+        <v>9600</v>
       </c>
       <c r="J20" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-69000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-41100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-35200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-30500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-30600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-18600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-20000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-19900</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E21" s="3">
         <v>45700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>41100</v>
       </c>
-      <c r="F21" s="3">
-        <v>42000</v>
-      </c>
       <c r="G21" s="3">
-        <v>47200</v>
+        <v>45100</v>
       </c>
       <c r="H21" s="3">
-        <v>51400</v>
+        <v>50600</v>
       </c>
       <c r="I21" s="3">
-        <v>55800</v>
+        <v>54300</v>
       </c>
       <c r="J21" s="3">
+        <v>61900</v>
+      </c>
+      <c r="K21" s="3">
         <v>10800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>19400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>21900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>24600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>18400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>15400</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>13600</v>
       </c>
       <c r="R21" s="3">
         <v>13600</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1393,108 +1433,117 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E23" s="3">
         <v>37500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>32900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>33800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>38400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>42600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>47100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>17700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>20100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>22900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>17300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14400</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>12500</v>
       </c>
       <c r="R23" s="3">
         <v>12500</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E24" s="3">
         <v>7800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1592,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E26" s="3">
         <v>29800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>26100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>27300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>30900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>35200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>37100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>18700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>11700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E27" s="3">
         <v>29800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>26100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>27300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>30900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>35200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>37100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>18700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>11700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1751,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1804,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1857,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1910,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>65800</v>
+        <v>-8000</v>
       </c>
       <c r="E32" s="3">
-        <v>65100</v>
+        <v>-8500</v>
       </c>
       <c r="F32" s="3">
-        <v>71100</v>
+        <v>-8100</v>
       </c>
       <c r="G32" s="3">
-        <v>66100</v>
+        <v>-11400</v>
       </c>
       <c r="H32" s="3">
-        <v>63800</v>
+        <v>-8700</v>
       </c>
       <c r="I32" s="3">
-        <v>65100</v>
+        <v>-9600</v>
       </c>
       <c r="J32" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="K32" s="3">
         <v>69000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>41100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>35200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>30500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>30600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>18600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>21500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>20000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E33" s="3">
         <v>29800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>26100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>27300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>30900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>35200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>37100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>18700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2069,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E35" s="3">
         <v>29800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>26100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>27300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>30900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>35200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>37100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>18700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2203,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,131 +2224,138 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>110300</v>
+        <v>516200</v>
       </c>
       <c r="E41" s="3">
-        <v>74700</v>
+        <v>490300</v>
       </c>
       <c r="F41" s="3">
-        <v>121000</v>
+        <v>399700</v>
       </c>
       <c r="G41" s="3">
-        <v>95000</v>
+        <v>399200</v>
       </c>
       <c r="H41" s="3">
-        <v>105900</v>
+        <v>302300</v>
       </c>
       <c r="I41" s="3">
-        <v>99200</v>
+        <v>304100</v>
       </c>
       <c r="J41" s="3">
+        <v>263300</v>
+      </c>
+      <c r="K41" s="3">
         <v>67100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>42000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>47700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>27700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>50600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>49700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>52500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>395000</v>
+        <v>4400</v>
       </c>
       <c r="E42" s="3">
-        <v>341100</v>
+        <v>6900</v>
       </c>
       <c r="F42" s="3">
-        <v>303300</v>
+        <v>7400</v>
       </c>
       <c r="G42" s="3">
-        <v>236300</v>
+        <v>6700</v>
       </c>
       <c r="H42" s="3">
-        <v>222700</v>
+        <v>10200</v>
       </c>
       <c r="I42" s="3">
-        <v>183800</v>
+        <v>8900</v>
       </c>
       <c r="J42" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K42" s="3">
         <v>319700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>347100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>460100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>740400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>940200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>965500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>755500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>571000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>509800</v>
       </c>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2288,31 +2381,34 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>2500</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2338,31 +2434,34 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>39500</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>43300</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>45500</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>44200</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>43500</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>42100</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>42400</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2388,31 +2487,34 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>560100</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>543100</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>452600</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>450200</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>356000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>355000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>313200</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2438,31 +2540,34 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>1711900</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>1646100</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>1539200</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>1420700</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>1444000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>1502700</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>1538900</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2488,108 +2593,117 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>113700</v>
+      </c>
+      <c r="E48" s="3">
         <v>114000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>115700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>118700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>119300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>119100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>124700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>126800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>66600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>67300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>67500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>69600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>70800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>72500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>73500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>74400</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>595400</v>
+      </c>
+      <c r="E49" s="3">
         <v>601600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>607800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>614000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>620300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>627100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>633900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>640800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>84100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>84300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>84500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>84600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>84700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>84800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>84900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2752,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,58 +2805,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="D52" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>199800</v>
+      </c>
+      <c r="F52" s="3">
+        <v>202100</v>
+      </c>
+      <c r="G52" s="3">
+        <v>157500</v>
+      </c>
+      <c r="H52" s="3">
+        <v>214900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>205900</v>
+      </c>
+      <c r="J52" s="3">
+        <v>204100</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3">
         <v>29600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>22700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10000</v>
-      </c>
-      <c r="O52" s="3">
-        <v>9800</v>
       </c>
       <c r="P52" s="3">
         <v>9800</v>
       </c>
       <c r="Q52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="R52" s="3">
         <v>11000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,58 +2911,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10629800</v>
+      </c>
+      <c r="E54" s="3">
         <v>10723700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10729200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10647100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10665500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10778400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10604700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10900400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4271800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4322300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4446000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4486000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4209100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4066500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4028600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3949200</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2987,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,35 +3008,36 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12300</v>
+        <v>8742600</v>
       </c>
       <c r="E57" s="3">
-        <v>12200</v>
+        <v>8725300</v>
       </c>
       <c r="F57" s="3">
-        <v>11300</v>
+        <v>8794700</v>
       </c>
       <c r="G57" s="3">
-        <v>7600</v>
+        <v>8873500</v>
       </c>
       <c r="H57" s="3">
-        <v>4600</v>
+        <v>8686600</v>
       </c>
       <c r="I57" s="3">
-        <v>3900</v>
+        <v>8766400</v>
       </c>
       <c r="J57" s="3">
+        <v>8738900</v>
+      </c>
+      <c r="K57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>5</v>
       </c>
@@ -2919,8 +3050,8 @@
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="P57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -2928,31 +3059,34 @@
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>65400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>249000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>225700</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>11100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>335400</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>381100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>249800</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2978,81 +3112,87 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>19000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>19700</v>
-      </c>
-      <c r="F59" s="3">
-        <v>20700</v>
-      </c>
-      <c r="G59" s="3">
-        <v>20200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>21100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>22200</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>23100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>8824900</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>8986600</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>9032600</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>8895900</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>9029600</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>9152000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>8992500</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3078,35 +3218,38 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>350000</v>
+        <v>128100</v>
       </c>
       <c r="E61" s="3">
-        <v>324900</v>
+        <v>126900</v>
       </c>
       <c r="F61" s="3">
-        <v>159800</v>
+        <v>126200</v>
       </c>
       <c r="G61" s="3">
-        <v>433600</v>
+        <v>176000</v>
       </c>
       <c r="H61" s="3">
-        <v>479500</v>
+        <v>128700</v>
       </c>
       <c r="I61" s="3">
-        <v>348400</v>
+        <v>128400</v>
       </c>
       <c r="J61" s="3">
+        <v>128300</v>
+      </c>
+      <c r="K61" s="3">
         <v>173300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3128,31 +3271,34 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>50600</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>44400</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>39700</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>54300</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>46300</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>39300</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>37700</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3178,8 +3324,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3377,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3430,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,58 +3483,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9003700</v>
+      </c>
+      <c r="E66" s="3">
         <v>9157900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9198500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9126100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9204600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9319700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9158500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9517300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3770400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3795600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3906300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3923900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3644500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3510300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3483300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3402800</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3559,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3610,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3663,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3716,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,58 +3769,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>474900</v>
+      </c>
+      <c r="E72" s="3">
         <v>447900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>425100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>405900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>385600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>361600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>333400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>303100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>262800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>253200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>244700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>237200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>241000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>229800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>221300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>214500</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3875,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3928,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,58 +3981,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1626100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1565800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1530700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1521000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1460800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1458700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1446200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1383200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>501400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>526700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>539700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>562100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>564600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>556200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>545300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>546500</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4087,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E81" s="3">
         <v>29800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>26100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>27300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>30900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>35200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>37100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>18700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,46 +4221,47 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8200</v>
+        <v>2000</v>
       </c>
       <c r="E83" s="3">
-        <v>8200</v>
+        <v>1800</v>
       </c>
       <c r="F83" s="3">
-        <v>8200</v>
+        <v>1800</v>
       </c>
       <c r="G83" s="3">
-        <v>8800</v>
+        <v>1900</v>
       </c>
       <c r="H83" s="3">
-        <v>8700</v>
+        <v>1000</v>
       </c>
       <c r="I83" s="3">
-        <v>8700</v>
+        <v>1000</v>
       </c>
       <c r="J83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K83" s="3">
         <v>8400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>1900</v>
       </c>
       <c r="L83" s="3">
         <v>1900</v>
       </c>
       <c r="M83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N83" s="3">
         <v>2000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>1100</v>
       </c>
       <c r="P83" s="3">
         <v>1100</v>
@@ -4073,8 +4272,11 @@
       <c r="R83" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4325,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4378,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4431,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4484,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4537,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E89" s="3">
         <v>38100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>31100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>31300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>38900</v>
-      </c>
-      <c r="H89" s="3">
-        <v>49000</v>
       </c>
       <c r="I89" s="3">
         <v>49000</v>
       </c>
       <c r="J89" s="3">
+        <v>49000</v>
+      </c>
+      <c r="K89" s="3">
         <v>34900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>33300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>24800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>16100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-20200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>30500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>15900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,49 +4613,50 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-1200</v>
       </c>
       <c r="I91" s="3">
         <v>-1200</v>
       </c>
       <c r="J91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-200</v>
       </c>
       <c r="M91" s="3">
         <v>-200</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-300</v>
       </c>
       <c r="Q91" s="3">
         <v>-300</v>
@@ -4443,8 +4664,11 @@
       <c r="R91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4717,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,58 +4770,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>138900</v>
+      </c>
+      <c r="E94" s="3">
         <v>103300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-109600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>160500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>91600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-159900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>203000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>511100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-203200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-61900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-172300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-324600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>69000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>146300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-24700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,43 +4846,44 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F96" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="H96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K96" s="3">
         <v>-6900</v>
       </c>
-      <c r="E96" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-2900</v>
       </c>
       <c r="M96" s="3">
         <v>-2900</v>
       </c>
       <c r="N96" s="3">
-        <v>-3200</v>
+        <v>-2900</v>
       </c>
       <c r="O96" s="3">
         <v>-3200</v>
@@ -4658,13 +4892,16 @@
         <v>-3200</v>
       </c>
       <c r="Q96" s="3">
-        <v>-2500</v>
+        <v>-3200</v>
       </c>
       <c r="R96" s="3">
         <v>-2500</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>-2500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4950,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5003,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,81 +5056,87 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-172500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-50900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>79000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-94900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-132300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>151700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-360400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-386500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-48400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-246100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>112400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>296200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>110800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>28800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>75400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>123600</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4913,54 +5162,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E102" s="3">
         <v>90500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>97000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>40800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-108400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>193900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-115000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-406500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-58100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-48600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>210400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>183700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>66700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>160400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
   <si>
     <t>STEL</t>
   </si>
@@ -656,145 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E8" s="3">
         <v>113800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>108800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>104300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>111800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>109100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>111800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>119700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>132000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>67900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>62800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>60300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>32500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>32300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -846,35 +852,38 @@
       <c r="S9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E10" s="3">
         <v>113800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>108800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>104300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>111800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>109100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>111800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>119700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -899,8 +908,11 @@
       <c r="S10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -973,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1026,8 +1042,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1040,21 +1059,21 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>3100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1079,16 +1098,19 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E15" s="3">
         <v>8100</v>
-      </c>
-      <c r="E15" s="3">
-        <v>8200</v>
       </c>
       <c r="F15" s="3">
         <v>8200</v>
@@ -1097,28 +1119,28 @@
         <v>8200</v>
       </c>
       <c r="H15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I15" s="3">
         <v>8800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>8700</v>
       </c>
       <c r="J15" s="3">
         <v>8700</v>
       </c>
       <c r="K15" s="3">
+        <v>8700</v>
+      </c>
+      <c r="L15" s="3">
         <v>-9000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>-1900</v>
       </c>
       <c r="M15" s="3">
         <v>-1900</v>
       </c>
       <c r="N15" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="O15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>-1100</v>
       </c>
       <c r="P15" s="3">
         <v>-1100</v>
@@ -1132,8 +1154,11 @@
       <c r="S15" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E17" s="3">
         <v>63100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>62700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>63300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>63500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>58600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>56700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>58300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>61100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-3600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E18" s="3">
         <v>50700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>41000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>48300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>50500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>55200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>61400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>70900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>58700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>55300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>53400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>31900</v>
-      </c>
-      <c r="P18" s="3">
-        <v>35900</v>
       </c>
       <c r="Q18" s="3">
         <v>35900</v>
       </c>
       <c r="R18" s="3">
-        <v>32500</v>
+        <v>35900</v>
       </c>
       <c r="S18" s="3">
         <v>32500</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,114 +1309,121 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E20" s="3">
         <v>8000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>11400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-69000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-41100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-35200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-30500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-30600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-21500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-20000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-19900</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E21" s="3">
         <v>50900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>45700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>41100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>45100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>50600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>54300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>61900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>19400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>21900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>24600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>18400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>15400</v>
-      </c>
-      <c r="R21" s="3">
-        <v>13600</v>
       </c>
       <c r="S21" s="3">
         <v>13600</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1409,8 +1448,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1436,114 +1475,123 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E23" s="3">
         <v>42700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>37500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>32900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>33800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>38400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>42600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>47100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>17700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>20100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>22900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>17300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>14400</v>
-      </c>
-      <c r="R23" s="3">
-        <v>12500</v>
       </c>
       <c r="S23" s="3">
         <v>12500</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E24" s="3">
         <v>8800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E26" s="3">
         <v>33900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>29800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>26100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>27300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>30900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>35200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>37100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E27" s="3">
         <v>33900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>29800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>26100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>27300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>30900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>35200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>37100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>14400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1807,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-11400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>69000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>41100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>35200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>30500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>30600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>18600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>21500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>20000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E33" s="3">
         <v>33900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>29800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>26100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>27300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>30900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>35200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>37100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>14400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E35" s="3">
         <v>33900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>29800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>26100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>27300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>30900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>35200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>37100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>14400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,114 +2310,121 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>911200</v>
+      </c>
+      <c r="E41" s="3">
         <v>516200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>490300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>399700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>399200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>302300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>304100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>263300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>67100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>41200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>42000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>47700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>27700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>50600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>49700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>52500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E42" s="3">
         <v>4400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>319700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>347100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>460100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>740400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>940200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>965500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>755500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>571000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>509800</v>
       </c>
     </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2357,8 +2449,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2384,20 +2476,23 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3">
         <v>2500</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2410,8 +2505,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2437,35 +2532,38 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E45" s="3">
         <v>39500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>43300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>45500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>44200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>43500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>42100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>42400</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2490,35 +2588,38 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>955400</v>
+      </c>
+      <c r="E46" s="3">
         <v>560100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>543100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>452600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>450200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>356000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>355000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>313200</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2543,35 +2644,38 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1681200</v>
+      </c>
+      <c r="E47" s="3">
         <v>1711900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1646100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1539200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1420700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1444000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1502700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1538900</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2596,114 +2700,123 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E48" s="3">
         <v>113700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>114000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>115700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>118700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>119300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>119100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>124700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>126800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>66600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>67300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>67500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>69600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>70800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>72500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>73500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>74400</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>589900</v>
+      </c>
+      <c r="E49" s="3">
         <v>595400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>601600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>607800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>614000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>620300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>627100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>633900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>640800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>84100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>84300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>84500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>84600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>84700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>84800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>84900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,61 +2924,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>157500</v>
+      </c>
+      <c r="E52" s="3">
         <v>182000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>199800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>202100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>157500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>214900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>205900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>204100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3">
         <v>29600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>22700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10000</v>
-      </c>
-      <c r="P52" s="3">
-        <v>9800</v>
       </c>
       <c r="Q52" s="3">
         <v>9800</v>
       </c>
       <c r="R52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="S52" s="3">
         <v>11000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10905800</v>
+      </c>
+      <c r="E54" s="3">
         <v>10629800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10723700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10729200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10647100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10665500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10778400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10604700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10900400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4271800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4322300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4446000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4486000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4209100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4066500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4028600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3949200</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,38 +3138,39 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9128400</v>
+      </c>
+      <c r="E57" s="3">
         <v>8742600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8725300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8794700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8873500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8686600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8766400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8738900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3053,8 +3183,8 @@
       <c r="P57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -3062,35 +3192,38 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E58" s="3">
         <v>65400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>249000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>225700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>335400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>381100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>249800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3115,8 +3248,11 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3141,62 +3277,65 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>23100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9155900</v>
+      </c>
+      <c r="E60" s="3">
         <v>8824900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8986600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9032600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8895900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9029600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9152000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8992500</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3221,38 +3360,41 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>84200</v>
+      </c>
+      <c r="E61" s="3">
         <v>128100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>126900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>126200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>176000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>128700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>128400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>128300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>173300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3274,35 +3416,38 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E62" s="3">
         <v>50600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>44400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>39700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>54300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>46300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>39300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>37700</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -3327,8 +3472,11 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9297900</v>
+      </c>
+      <c r="E66" s="3">
         <v>9003700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9157900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9198500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9126100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9204600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9319700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9158500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9517300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3770400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3795600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3906300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3923900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3644500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3510300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3483300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3402800</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3719,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>492600</v>
+      </c>
+      <c r="E72" s="3">
         <v>474900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>447900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>425100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>405900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>385600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>361600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>333400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>303100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>262800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>253200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>244700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>237200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>241000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>229800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>221300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>214500</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1607900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1626100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1565800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1530700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1521000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1460800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1458700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1446200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1383200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>501400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>526700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>539700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>562100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>564600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>556200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>545300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>546500</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E81" s="3">
         <v>33900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>29800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>26100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>27300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>30900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>35200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>37100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>14400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,8 +4419,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4231,16 +4429,16 @@
         <v>2000</v>
       </c>
       <c r="E83" s="3">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="F83" s="3">
         <v>1800</v>
       </c>
       <c r="G83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H83" s="3">
         <v>1900</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1000</v>
       </c>
       <c r="I83" s="3">
         <v>1000</v>
@@ -4249,22 +4447,22 @@
         <v>1000</v>
       </c>
       <c r="K83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L83" s="3">
         <v>8400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>1900</v>
       </c>
       <c r="M83" s="3">
         <v>1900</v>
       </c>
       <c r="N83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O83" s="3">
         <v>2000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>1100</v>
       </c>
       <c r="Q83" s="3">
         <v>1100</v>
@@ -4275,8 +4473,11 @@
       <c r="S83" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E89" s="3">
         <v>59500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>31100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>31300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>38900</v>
-      </c>
-      <c r="I89" s="3">
-        <v>49000</v>
       </c>
       <c r="J89" s="3">
         <v>49000</v>
       </c>
       <c r="K89" s="3">
+        <v>49000</v>
+      </c>
+      <c r="L89" s="3">
         <v>34900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>33300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>24800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>16100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-20200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>30500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>15900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,52 +4833,53 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-1200</v>
       </c>
       <c r="J91" s="3">
         <v>-1200</v>
       </c>
       <c r="K91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L91" s="3">
         <v>-3100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-200</v>
       </c>
       <c r="N91" s="3">
         <v>-200</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-300</v>
       </c>
       <c r="R91" s="3">
         <v>-300</v>
@@ -4667,8 +4887,11 @@
       <c r="S91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>113500</v>
+      </c>
+      <c r="E94" s="3">
         <v>138900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>103300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-109600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>160500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>91600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-159900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>203000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>511100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-203200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-61900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-172300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-324600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>69000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>146300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-24700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,22 +5079,23 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>6900</v>
+        <v>7500</v>
       </c>
       <c r="E96" s="3">
         <v>6900</v>
       </c>
       <c r="F96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="G96" s="3">
         <v>7000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>6900</v>
       </c>
       <c r="H96" s="3">
         <v>6900</v>
@@ -4874,19 +5107,19 @@
         <v>6900</v>
       </c>
       <c r="K96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="L96" s="3">
         <v>-6900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-2900</v>
       </c>
       <c r="N96" s="3">
         <v>-2900</v>
       </c>
       <c r="O96" s="3">
-        <v>-3200</v>
+        <v>-2900</v>
       </c>
       <c r="P96" s="3">
         <v>-3200</v>
@@ -4895,13 +5128,16 @@
         <v>-3200</v>
       </c>
       <c r="R96" s="3">
-        <v>-2500</v>
+        <v>-3200</v>
       </c>
       <c r="S96" s="3">
         <v>-2500</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>-2500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,61 +5301,67 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>277600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-172500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-50900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>79000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-94900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-132300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>151700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-360400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-386500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-48400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-246100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>112400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>296200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>110800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>28800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>75400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>123600</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5138,8 +5386,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -5165,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>395000</v>
+      </c>
+      <c r="E102" s="3">
         <v>26000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>90500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>97000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>40800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-108400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>193900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-115000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-406500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-58100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-48600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>210400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>183700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>66700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>160400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>STEL</t>
   </si>
@@ -656,151 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>101100</v>
+      </c>
+      <c r="E8" s="3">
         <v>107000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>113800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>108800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>104300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>111800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>109100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>111800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>119700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>132000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>67900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>62800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>60300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>32100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>32500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>32300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -855,38 +862,41 @@
       <c r="T9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>101100</v>
+      </c>
+      <c r="E10" s="3">
         <v>107000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>113800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>108800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>104300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>111800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>109100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>111800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>119700</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -911,8 +921,11 @@
       <c r="T10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,8 +1062,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1062,21 +1082,21 @@
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>3100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1101,19 +1121,22 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E15" s="3">
         <v>7600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>8200</v>
       </c>
       <c r="G15" s="3">
         <v>8200</v>
@@ -1122,28 +1145,28 @@
         <v>8200</v>
       </c>
       <c r="I15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="J15" s="3">
         <v>8800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>8700</v>
       </c>
       <c r="K15" s="3">
         <v>8700</v>
       </c>
       <c r="L15" s="3">
+        <v>8700</v>
+      </c>
+      <c r="M15" s="3">
         <v>-9000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>-1900</v>
       </c>
       <c r="N15" s="3">
         <v>-1900</v>
       </c>
       <c r="O15" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="P15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>-1100</v>
       </c>
       <c r="Q15" s="3">
         <v>-1100</v>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E17" s="3">
         <v>68000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>63100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>62700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>63300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>63500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>58600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>56700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>58300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>61100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-3400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-3600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E18" s="3">
         <v>39000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>50700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>46100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>41000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>48300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>50500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>55200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>61400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>70900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>58700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>55300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>53400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>31900</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>35900</v>
       </c>
       <c r="R18" s="3">
         <v>35900</v>
       </c>
       <c r="S18" s="3">
-        <v>32500</v>
+        <v>35900</v>
       </c>
       <c r="T18" s="3">
         <v>32500</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,120 +1343,127 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E20" s="3">
         <v>7200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>11400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>9600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-69000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-41100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-35200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-30500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-18600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-21500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-20000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-19900</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E21" s="3">
         <v>39300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>50900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>45700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>41100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>45100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>50600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>54300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>61900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>19400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>21900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>24600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>18400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>15400</v>
-      </c>
-      <c r="S21" s="3">
-        <v>13600</v>
       </c>
       <c r="T21" s="3">
         <v>13600</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1451,8 +1491,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1478,120 +1518,129 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E23" s="3">
         <v>31800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>42700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>37500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>32900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>33800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>38400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>42600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>47100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>17700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>22900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>17300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>14400</v>
-      </c>
-      <c r="S23" s="3">
-        <v>12500</v>
       </c>
       <c r="T23" s="3">
         <v>12500</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E24" s="3">
         <v>6600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E26" s="3">
         <v>25200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>33900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>29800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>26100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>27300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>30900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>35200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>37100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>18700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>14400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>11700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E27" s="3">
         <v>25200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>33900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>29800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>26100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>27300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>30900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>35200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>37100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>14400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-11400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-9600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>69000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>41100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>35200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>30500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>30600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>18600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>21500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>20000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E33" s="3">
         <v>25200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>33900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>29800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>26100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>27300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>30900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>35200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>37100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>14400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E35" s="3">
         <v>25200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>33900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>29800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>26100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>27300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>30900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>35200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>37100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>14400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,120 +2397,127 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>560600</v>
+      </c>
+      <c r="E41" s="3">
         <v>911200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>516200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>490300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>399700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>399200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>302300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>304100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>263300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>67100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>41200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>42000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>47700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>27700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>50600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>49700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>52500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E42" s="3">
         <v>6300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>319700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>347100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>460100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>740400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>940200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>965500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>755500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>571000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>509800</v>
       </c>
     </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2452,8 +2545,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2479,23 +2572,26 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
+      <c r="D44" s="3">
+        <v>5200</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3">
         <v>2500</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2508,8 +2604,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2535,38 +2631,41 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E45" s="3">
         <v>37900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>39500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>43300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>45500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>44200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>43500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>42100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>42400</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2591,38 +2690,41 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>608400</v>
+      </c>
+      <c r="E46" s="3">
         <v>955400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>560100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>543100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>452600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>450200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>356000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>355000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>313200</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2647,38 +2749,41 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1740300</v>
+      </c>
+      <c r="E47" s="3">
         <v>1681200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1711900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1646100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1539200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1420700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1444000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1502700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1538900</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2703,120 +2808,129 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>109800</v>
+      </c>
+      <c r="E48" s="3">
         <v>111900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>113700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>114000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>115700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>118700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>119300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>119100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>124700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>126800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>66600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>67300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>67500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>69600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>70800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>72500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>73500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>74400</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>584300</v>
+      </c>
+      <c r="E49" s="3">
         <v>589900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>595400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>601600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>607800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>614000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>620300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>627100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>633900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>640800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>84100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>84300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>84500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>84600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>84700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>84800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>84900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,64 +3044,70 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>192700</v>
+      </c>
+      <c r="E52" s="3">
         <v>157500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>182000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>199800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>202100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>157500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>214900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>205900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>204100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3">
         <v>29600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>22700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10000</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>9800</v>
       </c>
       <c r="R52" s="3">
         <v>9800</v>
       </c>
       <c r="S52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="T52" s="3">
         <v>11000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10434900</v>
+      </c>
+      <c r="E54" s="3">
         <v>10905800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10629800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10723700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10729200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10647100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10665500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10778400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10604700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10900400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4271800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4322300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4446000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4486000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4209100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4066500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4028600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3949200</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,41 +3269,42 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8562700</v>
+      </c>
+      <c r="E57" s="3">
         <v>9128400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8742600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8725300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8794700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8873500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8686600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8766400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8738900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3186,8 +3317,8 @@
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="R57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -3195,38 +3326,41 @@
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E58" s="3">
         <v>10400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>65400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>249000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>225700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>335400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>381100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>249800</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3251,8 +3385,11 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3280,65 +3417,68 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>23100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8700600</v>
+      </c>
+      <c r="E60" s="3">
         <v>9155900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8824900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8986600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9032600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8895900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9029600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9152000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8992500</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3363,41 +3503,44 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E61" s="3">
         <v>84200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>128100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>126900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>126200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>176000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>128700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>128400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>128300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>173300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3419,38 +3562,41 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E62" s="3">
         <v>57800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>50600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>44400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>39700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>54300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>46300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>39300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>37700</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8824100</v>
+      </c>
+      <c r="E66" s="3">
         <v>9297900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9003700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9157900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9198500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9126100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9204600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9319700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9158500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9517300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3770400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3795600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3906300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3923900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3644500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3510300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3483300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3402800</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>510100</v>
+      </c>
+      <c r="E72" s="3">
         <v>492600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>474900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>447900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>425100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>405900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>385600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>361600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>333400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>303100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>262800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>253200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>244700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>237200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>241000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>229800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>221300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>214500</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1610800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1607900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1626100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1565800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1530700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1521000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1460800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1458700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1446200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1383200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>501400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>526700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>539700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>562100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>564600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>556200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>545300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>546500</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E81" s="3">
         <v>25200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>33900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>29800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>26100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>27300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>30900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>35200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>37100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>14400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4432,16 +4631,16 @@
         <v>2000</v>
       </c>
       <c r="F83" s="3">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="G83" s="3">
         <v>1800</v>
       </c>
       <c r="H83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I83" s="3">
         <v>1900</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1000</v>
       </c>
       <c r="J83" s="3">
         <v>1000</v>
@@ -4450,22 +4649,22 @@
         <v>1000</v>
       </c>
       <c r="L83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M83" s="3">
         <v>8400</v>
-      </c>
-      <c r="M83" s="3">
-        <v>1900</v>
       </c>
       <c r="N83" s="3">
         <v>1900</v>
       </c>
       <c r="O83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P83" s="3">
         <v>2000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1100</v>
       </c>
       <c r="R83" s="3">
         <v>1100</v>
@@ -4476,8 +4675,11 @@
       <c r="T83" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E89" s="3">
         <v>3900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>59500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>31100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>31300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>38900</v>
-      </c>
-      <c r="J89" s="3">
-        <v>49000</v>
       </c>
       <c r="K89" s="3">
         <v>49000</v>
       </c>
       <c r="L89" s="3">
+        <v>49000</v>
+      </c>
+      <c r="M89" s="3">
         <v>34900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>33300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>24800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>16100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>30500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>8600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>15900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,55 +5054,56 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-1200</v>
       </c>
       <c r="K91" s="3">
         <v>-1200</v>
       </c>
       <c r="L91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M91" s="3">
         <v>-3100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-200</v>
       </c>
       <c r="O91" s="3">
         <v>-200</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-300</v>
       </c>
       <c r="S91" s="3">
         <v>-300</v>
@@ -4890,8 +5111,11 @@
       <c r="T91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>147400</v>
+      </c>
+      <c r="E94" s="3">
         <v>113500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>138900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>103300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-109600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>160500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>91600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-159900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>203000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>511100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-203200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-61900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-172300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-324600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>69000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>146300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-24700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,25 +5313,26 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E96" s="3">
         <v>7500</v>
-      </c>
-      <c r="E96" s="3">
-        <v>6900</v>
       </c>
       <c r="F96" s="3">
         <v>6900</v>
       </c>
       <c r="G96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="H96" s="3">
         <v>7000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>6900</v>
       </c>
       <c r="I96" s="3">
         <v>6900</v>
@@ -5110,19 +5344,19 @@
         <v>6900</v>
       </c>
       <c r="L96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="M96" s="3">
         <v>-6900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-2900</v>
       </c>
       <c r="O96" s="3">
         <v>-2900</v>
       </c>
       <c r="P96" s="3">
-        <v>-3200</v>
+        <v>-2900</v>
       </c>
       <c r="Q96" s="3">
         <v>-3200</v>
@@ -5131,13 +5365,16 @@
         <v>-3200</v>
       </c>
       <c r="S96" s="3">
-        <v>-2500</v>
+        <v>-3200</v>
       </c>
       <c r="T96" s="3">
         <v>-2500</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>-2500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5547,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-492300</v>
+      </c>
+      <c r="E100" s="3">
         <v>277600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-172500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-50900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>79000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-94900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-132300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>151700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-360400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-386500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-48400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-246100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>112400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>296200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>110800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>28800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>75400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>123600</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5389,8 +5638,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5416,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-350600</v>
+      </c>
+      <c r="E102" s="3">
         <v>395000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>26000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>90500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>97000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>40800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-108400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>193900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-115000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-406500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-58100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-48600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>210400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>183700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>66700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>160400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
   <si>
     <t>STEL</t>
   </si>
@@ -656,158 +656,165 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E8" s="3">
         <v>101100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>107000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>113800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>108800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>104300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>111800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>109100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>111800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>119700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>132000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>67900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>62800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>60300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>32100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>32500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>32300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -865,41 +872,44 @@
       <c r="U9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E10" s="3">
         <v>101100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>107000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>113800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>108800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>104300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>111800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>109100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>111800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>119700</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -924,8 +934,11 @@
       <c r="U10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,8 +960,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,8 +1082,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1085,21 +1105,21 @@
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>3100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1124,8 +1144,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1133,13 +1156,13 @@
         <v>7500</v>
       </c>
       <c r="E15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F15" s="3">
         <v>7600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>8200</v>
       </c>
       <c r="H15" s="3">
         <v>8200</v>
@@ -1148,28 +1171,28 @@
         <v>8200</v>
       </c>
       <c r="J15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K15" s="3">
         <v>8800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>8700</v>
       </c>
       <c r="L15" s="3">
         <v>8700</v>
       </c>
       <c r="M15" s="3">
+        <v>8700</v>
+      </c>
+      <c r="N15" s="3">
         <v>-9000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>-1900</v>
       </c>
       <c r="O15" s="3">
         <v>-1900</v>
       </c>
       <c r="P15" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Q15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>-1100</v>
       </c>
       <c r="R15" s="3">
         <v>-1100</v>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,8 +1229,9 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1212,117 +1239,123 @@
         <v>62900</v>
       </c>
       <c r="E17" s="3">
+        <v>62900</v>
+      </c>
+      <c r="F17" s="3">
         <v>68000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>63100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>62700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>63300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>63500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>58600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>56700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>58300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>61100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-3400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-3600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E18" s="3">
         <v>38200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>39000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>50700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>46100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>41000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>48300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>50500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>55200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>61400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>70900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>58700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>55300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>53400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>31900</v>
-      </c>
-      <c r="R18" s="3">
-        <v>35900</v>
       </c>
       <c r="S18" s="3">
         <v>35900</v>
       </c>
       <c r="T18" s="3">
-        <v>32500</v>
+        <v>35900</v>
       </c>
       <c r="U18" s="3">
         <v>32500</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,126 +1377,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E20" s="3">
         <v>7300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>11400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-69000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-41100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-35200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-30600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-18600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-21500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-20000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-19900</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E21" s="3">
         <v>38500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>39300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>50900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>45700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>41100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>45100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>50600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>54300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>61900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>21900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>24600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>18400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>15400</v>
-      </c>
-      <c r="T21" s="3">
-        <v>13600</v>
       </c>
       <c r="U21" s="3">
         <v>13600</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1494,8 +1534,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1521,126 +1561,135 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E23" s="3">
         <v>31000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>31800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>42700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>37500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>32900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>33800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>38400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>42600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>47100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>17700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>20100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>22900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>17300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>14400</v>
-      </c>
-      <c r="T23" s="3">
-        <v>12500</v>
       </c>
       <c r="U23" s="3">
         <v>12500</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E24" s="3">
         <v>6300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E26" s="3">
         <v>24700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>25200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>33900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>29800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>26100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>27300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>30900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>35200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>37100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>18700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>14400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>11700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E27" s="3">
         <v>24700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>25200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>33900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>29800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>26100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>27300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>30900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>35200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>37100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>14400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>11700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2119,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-11400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>69000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>41100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>35200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>30500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>30600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>18600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>21500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>20000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E33" s="3">
         <v>24700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>25200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>33900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>29800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>26100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>27300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>30900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>35200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>37100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>14400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>11700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E35" s="3">
         <v>24700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>25200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>33900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>29800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>26100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>27300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>30900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>35200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>37100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>14400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>11700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,126 +2484,133 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>578100</v>
+      </c>
+      <c r="E41" s="3">
         <v>560600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>911200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>516200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>490300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>399700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>399200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>302300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>304100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>263300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>67100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>41200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>42000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>47700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>27700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>50600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>49700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>52500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E42" s="3">
         <v>5000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>10200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>319700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>347100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>460100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>740400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>940200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>965500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>755500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>571000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>509800</v>
       </c>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2548,8 +2641,8 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2575,26 +2668,29 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E44" s="3">
         <v>5200</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3">
         <v>2500</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2607,8 +2703,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2634,41 +2730,44 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E45" s="3">
         <v>37700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>37900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>39500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>43300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>45500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>44200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>43500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>42100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>42400</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -2693,41 +2792,44 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>625600</v>
+      </c>
+      <c r="E46" s="3">
         <v>608400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>955400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>560100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>543100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>452600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>450200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>356000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>355000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>313200</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -2752,41 +2854,44 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1776800</v>
+      </c>
+      <c r="E47" s="3">
         <v>1740300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1681200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1711900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1646100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1539200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1420700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1444000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1502700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1538900</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -2811,126 +2916,135 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>108600</v>
+      </c>
+      <c r="E48" s="3">
         <v>109800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>111900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>113700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>114000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>115700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>118700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>119300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>119100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>124700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>126800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>66600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>67300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>67500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>69600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>70800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>72500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>73500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>74400</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>578800</v>
+      </c>
+      <c r="E49" s="3">
         <v>584300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>589900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>595400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>601600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>607800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>614000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>620300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>627100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>633900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>640800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>84100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>84300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>84500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>84600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>84700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>84800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>84900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,67 +3164,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>199100</v>
+      </c>
+      <c r="E52" s="3">
         <v>192700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>157500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>182000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>199800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>202100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>157500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>214900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>205900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>204100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O52" s="3">
         <v>29600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>22700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10000</v>
-      </c>
-      <c r="R52" s="3">
-        <v>9800</v>
       </c>
       <c r="S52" s="3">
         <v>9800</v>
       </c>
       <c r="T52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="U52" s="3">
         <v>11000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3288,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10493000</v>
+      </c>
+      <c r="E54" s="3">
         <v>10434900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10905800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10629800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10723700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10729200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10647100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10665500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10778400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10604700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10900400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4271800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4322300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4446000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4486000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4209100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4066500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4028600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3949200</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,44 +3400,45 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8673600</v>
+      </c>
+      <c r="E57" s="3">
         <v>8562700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9128400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8742600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8725300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8794700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8873500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8686600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8766400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8738900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3320,8 +3451,8 @@
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
@@ -3329,41 +3460,44 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>76300</v>
+      </c>
+      <c r="E58" s="3">
         <v>128100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>65400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>249000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>225700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>335400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>381100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>249800</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -3388,8 +3522,11 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3420,68 +3557,71 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>23100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8757500</v>
+      </c>
+      <c r="E60" s="3">
         <v>8700600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9155900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8824900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8986600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9032600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8895900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9029600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9152000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8992500</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -3506,44 +3646,47 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>85200</v>
+      </c>
+      <c r="E61" s="3">
         <v>84500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>84200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>128100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>126900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>126200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>176000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>128700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>128400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>128300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>173300</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3565,41 +3708,44 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E62" s="3">
         <v>39000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>57800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>50600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>44400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>39700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>54300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>46300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>39300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>37700</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3956,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8889200</v>
+      </c>
+      <c r="E66" s="3">
         <v>8824100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9297900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9003700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9157900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9198500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9126100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9204600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9319700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9158500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9517300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3770400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3795600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3906300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3923900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3644500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3510300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3483300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3402800</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4290,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>529200</v>
+      </c>
+      <c r="E72" s="3">
         <v>510100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>492600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>474900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>447900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>425100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>405900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>385600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>361600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>333400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>303100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>262800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>253200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>244700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>237200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>241000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>229800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>221300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>214500</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4538,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1603800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1610800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1607900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1626100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1565800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1530700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1521000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1460800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1458700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1446200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1383200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>501400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>526700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>539700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>562100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>564600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>556200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>545300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>546500</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E81" s="3">
         <v>24700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>25200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>33900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>29800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>26100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>27300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>30900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>35200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>37100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>14400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>11700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,13 +4817,14 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="E83" s="3">
         <v>2000</v>
@@ -4634,16 +4833,16 @@
         <v>2000</v>
       </c>
       <c r="G83" s="3">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="H83" s="3">
         <v>1800</v>
       </c>
       <c r="I83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J83" s="3">
         <v>1900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1000</v>
       </c>
       <c r="K83" s="3">
         <v>1000</v>
@@ -4652,22 +4851,22 @@
         <v>1000</v>
       </c>
       <c r="M83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N83" s="3">
         <v>8400</v>
-      </c>
-      <c r="N83" s="3">
-        <v>1900</v>
       </c>
       <c r="O83" s="3">
         <v>1900</v>
       </c>
       <c r="P83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q83" s="3">
         <v>2000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>1100</v>
       </c>
       <c r="S83" s="3">
         <v>1100</v>
@@ -4678,8 +4877,11 @@
       <c r="U83" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>59500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>38100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>31100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>31300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>38900</v>
-      </c>
-      <c r="K89" s="3">
-        <v>49000</v>
       </c>
       <c r="L89" s="3">
         <v>49000</v>
       </c>
       <c r="M89" s="3">
+        <v>49000</v>
+      </c>
+      <c r="N89" s="3">
         <v>34900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>33300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>24800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>16100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-20200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>30500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>15900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,58 +5275,59 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-1200</v>
       </c>
       <c r="L91" s="3">
         <v>-1200</v>
       </c>
       <c r="M91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-3100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-200</v>
       </c>
       <c r="P91" s="3">
         <v>-200</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-300</v>
       </c>
       <c r="T91" s="3">
         <v>-300</v>
@@ -5114,8 +5335,11 @@
       <c r="U91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5459,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="E94" s="3">
         <v>147400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>113500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>138900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>103300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-109600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>160500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>91600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-159900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>203000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>511100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-203200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-61900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-172300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-324600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>69000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>146300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-24700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,28 +5547,29 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E96" s="3">
         <v>7300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>7500</v>
-      </c>
-      <c r="F96" s="3">
-        <v>6900</v>
       </c>
       <c r="G96" s="3">
         <v>6900</v>
       </c>
       <c r="H96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I96" s="3">
         <v>7000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>6900</v>
       </c>
       <c r="J96" s="3">
         <v>6900</v>
@@ -5347,19 +5581,19 @@
         <v>6900</v>
       </c>
       <c r="M96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="N96" s="3">
         <v>-6900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-2900</v>
       </c>
       <c r="P96" s="3">
         <v>-2900</v>
       </c>
       <c r="Q96" s="3">
-        <v>-3200</v>
+        <v>-2900</v>
       </c>
       <c r="R96" s="3">
         <v>-3200</v>
@@ -5368,13 +5602,16 @@
         <v>-3200</v>
       </c>
       <c r="T96" s="3">
-        <v>-2500</v>
+        <v>-3200</v>
       </c>
       <c r="U96" s="3">
         <v>-2500</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>-2500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,67 +5793,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-492300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>277600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-172500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-50900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>79000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-94900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-132300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>151700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-360400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-386500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-48400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-246100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>112400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>296200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>110800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>28800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>75400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>123600</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5641,8 +5890,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5668,63 +5917,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-350600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>395000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>26000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>90500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>97000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>40800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-108400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>193900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-115000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-406500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-58100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-48600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>210400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>183700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>66700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>160400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>STEL</t>
   </si>
@@ -656,172 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>103800</v>
+      </c>
+      <c r="E8" s="3">
         <v>105300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>103000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>101100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>107000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>113800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>108800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>104300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>111800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>109100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>111800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>119700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>132000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>67900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>62800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>60300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>32100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>32500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>32300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>34500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -885,47 +891,50 @@
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>103800</v>
+      </c>
+      <c r="E10" s="3">
         <v>105300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>103000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>101100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>107000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>113800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>108800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>104300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>111800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>109100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>111800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>119700</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -950,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1040,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1131,21 +1150,21 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>3100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1170,28 +1189,31 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E15" s="3">
         <v>7600</v>
-      </c>
-      <c r="E15" s="3">
-        <v>7500</v>
       </c>
       <c r="F15" s="3">
         <v>7500</v>
       </c>
       <c r="G15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="H15" s="3">
         <v>7600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>8200</v>
       </c>
       <c r="J15" s="3">
         <v>8200</v>
@@ -1200,28 +1222,28 @@
         <v>8200</v>
       </c>
       <c r="L15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="M15" s="3">
         <v>8800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>8700</v>
       </c>
       <c r="N15" s="3">
         <v>8700</v>
       </c>
       <c r="O15" s="3">
+        <v>8700</v>
+      </c>
+      <c r="P15" s="3">
         <v>-9000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>-1900</v>
       </c>
       <c r="Q15" s="3">
         <v>-1900</v>
       </c>
       <c r="R15" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="S15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>-1100</v>
       </c>
       <c r="T15" s="3">
         <v>-1100</v>
@@ -1235,8 +1257,11 @@
       <c r="W15" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E17" s="3">
         <v>65900</v>
-      </c>
-      <c r="E17" s="3">
-        <v>62900</v>
       </c>
       <c r="F17" s="3">
         <v>62900</v>
       </c>
       <c r="G17" s="3">
+        <v>62900</v>
+      </c>
+      <c r="H17" s="3">
         <v>68000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>63100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>62700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>63300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>63500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>58600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>56700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>58300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>61100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-3400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-3600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E18" s="3">
         <v>39400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>40100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>38200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>39000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>50700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>46100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>41000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>48300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>50500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>55200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>61400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>70900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>58700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>55300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>53400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>31900</v>
-      </c>
-      <c r="T18" s="3">
-        <v>35900</v>
       </c>
       <c r="U18" s="3">
         <v>35900</v>
       </c>
       <c r="V18" s="3">
-        <v>32500</v>
+        <v>35900</v>
       </c>
       <c r="W18" s="3">
         <v>32500</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,138 +1444,145 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E20" s="3">
         <v>7200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>9600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-69000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-41100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-35200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-30500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-30600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-18600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-21500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-20000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-19900</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E21" s="3">
         <v>39800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>40600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>38500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>39300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>50900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>45700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>41100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>45100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>50600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>54300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>61900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>19400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>24600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>18400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>15400</v>
-      </c>
-      <c r="V21" s="3">
-        <v>13600</v>
       </c>
       <c r="W21" s="3">
         <v>13600</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1580,8 +1619,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1607,138 +1646,147 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E23" s="3">
         <v>32200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>33000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>31000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>31800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>42700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>37500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>32900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>33800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>38400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>42600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>47100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>17700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>20100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>22900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>17300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>14400</v>
-      </c>
-      <c r="V23" s="3">
-        <v>12500</v>
       </c>
       <c r="W23" s="3">
         <v>12500</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E24" s="3">
         <v>6500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E26" s="3">
         <v>25700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>26400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>24700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>25200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>33900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>29800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>26100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>27300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>30900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>35200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>37100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>18700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>14400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>11700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>10000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E27" s="3">
         <v>25700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>26400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>24700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>25200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>33900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>29800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>26100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>27300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>30900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>35200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>37100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>14300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>14400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>11700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>10000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-9600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>69000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>41100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>35200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>30500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>30600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>18600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>21500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>20000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E33" s="3">
         <v>25700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>26400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>24700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>25200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>33900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>29800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>26100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>27300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>30900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>35200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>37100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>14300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>14400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>11700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>10000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E35" s="3">
         <v>25700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>26400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>24700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>25200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>33900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>29800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>26100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>27300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>30900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>35200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>37100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>14300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>14400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>11700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>10000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,138 +2657,145 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>419500</v>
+      </c>
+      <c r="E41" s="3">
         <v>728400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>578100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>560600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>911200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>516200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>490300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>399700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>399200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>302300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>304100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>263300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>67100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>41200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>42000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>47700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>27700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>50600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>49700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>52500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E42" s="3">
         <v>3900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>319700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>347100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>460100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>740400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>940200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>965500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>755500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>571000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>509800</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2740,8 +2832,8 @@
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2767,32 +2859,35 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E44" s="3">
         <v>7900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5200</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="H44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3">
         <v>2500</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2805,8 +2900,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2832,47 +2927,50 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E45" s="3">
         <v>34900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>35500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>37900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>39500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>43300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>45500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>44200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>43500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>42100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>42400</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -2897,47 +2995,50 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>467100</v>
+      </c>
+      <c r="E46" s="3">
         <v>775100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>625600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>608400</v>
       </c>
-      <c r="G46" s="3">
-        <v>955400</v>
-      </c>
       <c r="H46" s="3">
+        <v>957100</v>
+      </c>
+      <c r="I46" s="3">
         <v>560100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>543100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>452600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>450200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>356000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>355000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>313200</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -2962,47 +3063,50 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2244000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1887700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1776800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1740300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1681200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1711900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1646100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1539200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1420700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1444000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1502700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1538900</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -3027,138 +3131,147 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>106100</v>
+      </c>
+      <c r="E48" s="3">
         <v>107800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>108600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>109800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>111900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>113700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>114000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>115700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>118700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>119300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>119100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>124700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>126800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>66600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>67300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>67500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>69600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>70800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>72500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>73500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>74400</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>568300</v>
+      </c>
+      <c r="E49" s="3">
         <v>573200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>578800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>584300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>589900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>595400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>601600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>607800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>614000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>620300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>627100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>633900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>640800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>84100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>84300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>84500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>84600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>84700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>84800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>84900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,73 +3403,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E52" s="3">
         <v>195300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>199100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>192700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>155800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>182000</v>
+      </c>
+      <c r="J52" s="3">
+        <v>199800</v>
+      </c>
+      <c r="K52" s="3">
+        <v>202100</v>
+      </c>
+      <c r="L52" s="3">
         <v>157500</v>
       </c>
-      <c r="H52" s="3">
-        <v>182000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>199800</v>
-      </c>
-      <c r="J52" s="3">
-        <v>202100</v>
-      </c>
-      <c r="K52" s="3">
-        <v>157500</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>214900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>205900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>204100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="3">
         <v>29600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>22700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10000</v>
-      </c>
-      <c r="T52" s="3">
-        <v>9800</v>
       </c>
       <c r="U52" s="3">
         <v>9800</v>
       </c>
       <c r="V52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="W52" s="3">
         <v>11000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10806600</v>
+      </c>
+      <c r="E54" s="3">
         <v>10628100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10493000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10434900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10905800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10629800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10723700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10729200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10647100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10665500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10778400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10604700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10900400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4271800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4322300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4446000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4486000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4209100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4066500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4028600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3949200</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,50 +3661,51 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9021500</v>
+      </c>
+      <c r="E57" s="3">
         <v>8817500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8673600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8562700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9128400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8742600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8725300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8794700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8873500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8686600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8766400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8738900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3588,8 +3718,8 @@
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -3597,47 +3727,50 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E58" s="3">
         <v>4900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>76300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>128100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>65400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>249000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>225700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>335400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>381100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>249800</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -3662,8 +3795,11 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3700,74 +3836,77 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
         <v>23100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9035300</v>
+      </c>
+      <c r="E60" s="3">
         <v>8831800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8757500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8700600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9155900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8824900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8986600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9032600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8895900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9029600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9152000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8992500</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -3792,50 +3931,53 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E61" s="3">
         <v>86300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>85200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>84500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>84200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>128100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>126900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>126200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>176000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>128700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>128400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>128300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>173300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3857,47 +3999,50 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E62" s="3">
         <v>56800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>46500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>39000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>57800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>50600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>44400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>39700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>54300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>46300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>39300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>37700</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -3922,8 +4067,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9137900</v>
+      </c>
+      <c r="E66" s="3">
         <v>8975000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8889200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8824100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9297900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9003700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9157900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9198500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9126100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9204600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9319700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9158500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9517300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3770400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3795600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3906300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3923900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3644500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3510300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3483300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3402800</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>566200</v>
+      </c>
+      <c r="E72" s="3">
         <v>547700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>529200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>510100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>492600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>474900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>447900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>425100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>405900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>385600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>361600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>333400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>303100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>262800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>253200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>244700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>237200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>241000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>229800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>221300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>214500</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1668700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1653100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1603800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1610800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1607900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1626100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1565800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1530700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1521000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1460800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1458700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1446200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1383200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>501400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>526700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>539700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>562100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>564600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>556200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>545300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>546500</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E81" s="3">
         <v>25700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>26400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>24700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>25200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>33900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>29800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>26100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>27300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>30900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>35200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>37100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>14300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>14400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>11700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>10000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,19 +5214,20 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="E83" s="3">
         <v>1900</v>
       </c>
       <c r="F83" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="G83" s="3">
         <v>2000</v>
@@ -5038,16 +5236,16 @@
         <v>2000</v>
       </c>
       <c r="I83" s="3">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="J83" s="3">
         <v>1800</v>
       </c>
       <c r="K83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L83" s="3">
         <v>1900</v>
-      </c>
-      <c r="L83" s="3">
-        <v>1000</v>
       </c>
       <c r="M83" s="3">
         <v>1000</v>
@@ -5056,22 +5254,22 @@
         <v>1000</v>
       </c>
       <c r="O83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P83" s="3">
         <v>8400</v>
-      </c>
-      <c r="P83" s="3">
-        <v>1900</v>
       </c>
       <c r="Q83" s="3">
         <v>1900</v>
       </c>
       <c r="R83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="S83" s="3">
         <v>2000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>1100</v>
       </c>
       <c r="U83" s="3">
         <v>1100</v>
@@ -5082,8 +5280,11 @@
       <c r="W83" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E89" s="3">
         <v>63600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>25800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>59500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>38100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>31100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>31300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>38900</v>
-      </c>
-      <c r="M89" s="3">
-        <v>49000</v>
       </c>
       <c r="N89" s="3">
         <v>49000</v>
       </c>
       <c r="O89" s="3">
+        <v>49000</v>
+      </c>
+      <c r="P89" s="3">
         <v>34900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>33300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>24800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>16100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-20200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>30500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>15900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,64 +5716,65 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-1200</v>
       </c>
       <c r="N91" s="3">
         <v>-1200</v>
       </c>
       <c r="O91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="P91" s="3">
         <v>-3100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-200</v>
       </c>
       <c r="R91" s="3">
         <v>-200</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-300</v>
       </c>
       <c r="V91" s="3">
         <v>-300</v>
@@ -5562,8 +5782,11 @@
       <c r="W91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-478700</v>
+      </c>
+      <c r="E94" s="3">
         <v>24900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-41800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>147400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>113500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>138900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>103300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-109600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>160500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>91600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-159900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>203000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>511100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-203200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-61900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-172300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-324600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>69000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>146300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-24700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,34 +6014,35 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>7200</v>
+        <v>7600</v>
       </c>
       <c r="E96" s="3">
         <v>7200</v>
       </c>
       <c r="F96" s="3">
+        <v>7200</v>
+      </c>
+      <c r="G96" s="3">
         <v>7300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>7500</v>
-      </c>
-      <c r="H96" s="3">
-        <v>6900</v>
       </c>
       <c r="I96" s="3">
         <v>6900</v>
       </c>
       <c r="J96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K96" s="3">
         <v>7000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>6900</v>
       </c>
       <c r="L96" s="3">
         <v>6900</v>
@@ -5821,19 +6054,19 @@
         <v>6900</v>
       </c>
       <c r="O96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="P96" s="3">
         <v>-6900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-2900</v>
       </c>
       <c r="R96" s="3">
         <v>-2900</v>
       </c>
       <c r="S96" s="3">
-        <v>-3200</v>
+        <v>-2900</v>
       </c>
       <c r="T96" s="3">
         <v>-3200</v>
@@ -5842,13 +6075,16 @@
         <v>-3200</v>
       </c>
       <c r="V96" s="3">
-        <v>-2500</v>
+        <v>-3200</v>
       </c>
       <c r="W96" s="3">
         <v>-2500</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>-2500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>156400</v>
+      </c>
+      <c r="E100" s="3">
         <v>61800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>33500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-492300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>277600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-172500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-50900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>79000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-94900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-132300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>151700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-360400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-386500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-48400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-246100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>112400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>296200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>110800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>28800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>75400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>123600</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6145,8 +6393,8 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6172,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-309000</v>
+      </c>
+      <c r="E102" s="3">
         <v>150300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>17500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-350600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>395000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>26000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>90500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>97000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>40800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-108400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>193900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-115000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-406500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-58100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-48600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>210400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>183700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>66700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>160400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
   <si>
     <t>STEL</t>
   </si>
@@ -656,178 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>108500</v>
+      </c>
+      <c r="E8" s="3">
         <v>103800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>105300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>103000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>101100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>107000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>113800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>108800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>104300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>111800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>109100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>111800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>119700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>132000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>67900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>62800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>60300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>32100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>32500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>32300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -894,50 +901,53 @@
       <c r="X9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>108500</v>
+      </c>
+      <c r="E10" s="3">
         <v>103800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>105300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>103000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>101100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>107000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>113800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>108800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>104300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>111800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>109100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>111800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>119700</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -962,8 +972,11 @@
       <c r="X10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,13 +1141,16 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>3300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1153,21 +1173,21 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>3100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1192,31 +1212,34 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E15" s="3">
         <v>7000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7600</v>
-      </c>
-      <c r="F15" s="3">
-        <v>7500</v>
       </c>
       <c r="G15" s="3">
         <v>7500</v>
       </c>
       <c r="H15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I15" s="3">
         <v>7600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>8200</v>
       </c>
       <c r="K15" s="3">
         <v>8200</v>
@@ -1225,28 +1248,28 @@
         <v>8200</v>
       </c>
       <c r="M15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="N15" s="3">
         <v>8800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>8700</v>
       </c>
       <c r="O15" s="3">
         <v>8700</v>
       </c>
       <c r="P15" s="3">
+        <v>8700</v>
+      </c>
+      <c r="Q15" s="3">
         <v>-9000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>-1900</v>
       </c>
       <c r="R15" s="3">
         <v>-1900</v>
       </c>
       <c r="S15" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="T15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>-1100</v>
       </c>
       <c r="U15" s="3">
         <v>-1100</v>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E17" s="3">
         <v>66000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>65900</v>
-      </c>
-      <c r="F17" s="3">
-        <v>62900</v>
       </c>
       <c r="G17" s="3">
         <v>62900</v>
       </c>
       <c r="H17" s="3">
+        <v>62900</v>
+      </c>
+      <c r="I17" s="3">
         <v>68000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>63100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>62700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>63300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>63500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>58600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>56700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>58300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>61100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-3400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-3600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E18" s="3">
         <v>37700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>39400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>40100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>38200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>39000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>50700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>46100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>41000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>48300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>50500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>55200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>61400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>70900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>58700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>55300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>53400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>31900</v>
-      </c>
-      <c r="U18" s="3">
-        <v>35900</v>
       </c>
       <c r="V18" s="3">
         <v>35900</v>
       </c>
       <c r="W18" s="3">
-        <v>32500</v>
+        <v>35900</v>
       </c>
       <c r="X18" s="3">
         <v>32500</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,144 +1478,151 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E20" s="3">
         <v>6100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>11400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-69000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-41100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-35200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-30500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-30600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-18600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-21500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-20000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-19900</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E21" s="3">
         <v>38600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>39800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>40600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>38500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>39300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>50900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>45700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>41100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>45100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>50600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>54300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>61900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>19400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>21900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>24600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>18400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>15400</v>
-      </c>
-      <c r="W21" s="3">
-        <v>13600</v>
       </c>
       <c r="X21" s="3">
         <v>13600</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3">
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1622,8 +1662,8 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1649,144 +1689,153 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E23" s="3">
         <v>31600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>32200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>33000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>31000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>31800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>42700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>37500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>32900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>38400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>42600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>47100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>17700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>20100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>22900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>17300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>14400</v>
-      </c>
-      <c r="W23" s="3">
-        <v>12500</v>
       </c>
       <c r="X23" s="3">
         <v>12500</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E24" s="3">
         <v>5500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E26" s="3">
         <v>26100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>25700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>26400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>24700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>25200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>33900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>29800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>26100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>27300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>30900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>35200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>37100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>14300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>18700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>14400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>11700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>10000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E27" s="3">
         <v>26100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>25700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>26400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>24700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>25200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>33900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>29800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>26100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>27300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>30900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>35200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>37100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>14300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>16400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>14400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>11700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>10000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-11400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>69000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>41100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>35200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>30500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>30600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>18600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>21500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>20000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E33" s="3">
         <v>26100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>25700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>26400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>24700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>25200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>33900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>29800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>26100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>27300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>30900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>35200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>37100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>14300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>16400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>14400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>11700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>10000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E35" s="3">
         <v>26100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>25700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>26400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>24700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>25200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>33900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>29800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>26100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>27300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>30900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>35200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>37100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>14300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>16400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>14400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>11700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>10000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,144 +2744,151 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>549600</v>
+      </c>
+      <c r="E41" s="3">
         <v>419500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>728400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>578100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>560600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>911200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>516200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>490300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>399700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>399200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>302300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>304100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>263300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>67100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>41200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>42000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>47700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>27700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>50600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>49700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>52500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E42" s="3">
         <v>4300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>10200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>7500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>319700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>347100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>460100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>740400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>940200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>965500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>755500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>571000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>509800</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2835,8 +2928,8 @@
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2862,35 +2955,38 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E44" s="3">
         <v>7500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1700</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K44" s="3">
         <v>2500</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2903,8 +2999,8 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2930,50 +3026,53 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E45" s="3">
         <v>35900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>34900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>35500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>37700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>37900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>39500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>43300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>45500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>44200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>43500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>42100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>42400</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -2998,50 +3097,53 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>599700</v>
+      </c>
+      <c r="E46" s="3">
         <v>467100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>775100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>625600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>608400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>957100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>560100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>543100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>452600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>450200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>356000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>355000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>313200</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3066,50 +3168,53 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1915800</v>
+      </c>
+      <c r="E47" s="3">
         <v>2244000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1887700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1776800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1740300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1681200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1711900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1646100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1539200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1420700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1444000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1502700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1538900</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -3134,144 +3239,153 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>99900</v>
+      </c>
+      <c r="E48" s="3">
         <v>106100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>107800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>108600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>109800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>111900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>113700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>114000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>115700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>118700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>119300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>119100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>124700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>126800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>66600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>67300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>67500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>69600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>70800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>72500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>73500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>74400</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>563500</v>
+      </c>
+      <c r="E49" s="3">
         <v>568300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>573200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>578800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>584300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>589900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>595400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>601600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>607800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>614000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>620300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>627100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>633900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>640800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>84100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>84300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>84500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>84600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>84700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>84800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>84900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,76 +3523,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>208000</v>
+      </c>
+      <c r="E52" s="3">
         <v>165000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>195300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>199100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>192700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>155800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>182000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>199800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>202100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>157500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>214900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>205900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>204100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R52" s="3">
         <v>29600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>22700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10000</v>
-      </c>
-      <c r="U52" s="3">
-        <v>9800</v>
       </c>
       <c r="V52" s="3">
         <v>9800</v>
       </c>
       <c r="W52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="X52" s="3">
         <v>11000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3665,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10889400</v>
+      </c>
+      <c r="E54" s="3">
         <v>10806600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10628100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10493000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10434900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10905800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10629800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10723700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10729200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10647100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10665500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10778400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10604700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10900400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4271800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4322300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4446000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4486000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4209100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4066500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4028600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3949200</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,53 +3792,54 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8982000</v>
+      </c>
+      <c r="E57" s="3">
         <v>9021500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8817500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8673600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8562700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9128400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8742600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8725300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8794700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8873500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8686600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8766400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8738900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3721,8 +3852,8 @@
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
+      <c r="V57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
@@ -3730,50 +3861,53 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>142200</v>
+      </c>
+      <c r="E58" s="3">
         <v>8300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>76300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>128100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>65400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>249000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>225700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>335400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>381100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>249800</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -3798,8 +3932,11 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3839,77 +3976,80 @@
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="3">
         <v>23100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>16100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9129500</v>
+      </c>
+      <c r="E60" s="3">
         <v>9035300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8831800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8757500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8700600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9155900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8824900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8986600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9032600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8895900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9029600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9152000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8992500</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -3934,53 +4074,56 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>52600</v>
+      </c>
+      <c r="E61" s="3">
         <v>52400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>86300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>85200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>84500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>84200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>128100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>126900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>126200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>176000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>128700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>128400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>128300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>173300</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4002,50 +4145,53 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E62" s="3">
         <v>50200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>56800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>46500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>39000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>57800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>50600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>44400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>39700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>54300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>46300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>39300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>37700</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4429,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9221600</v>
+      </c>
+      <c r="E66" s="3">
         <v>9137900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8975000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8889200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8824100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9297900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9003700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9157900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9198500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9126100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9204600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9319700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9158500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9517300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3770400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3795600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3906300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3923900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3644500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3510300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3483300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3402800</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4811,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>585400</v>
+      </c>
+      <c r="E72" s="3">
         <v>566200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>547700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>529200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>510100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>492600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>474900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>447900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>425100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>405900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>385600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>361600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>333400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>303100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>262800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>253200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>244700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>237200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>241000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>229800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>221300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>214500</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5095,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1667800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1668700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1653100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1603800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1610800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1607900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1626100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1565800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1530700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1521000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1460800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1458700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1446200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1383200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>501400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>526700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>539700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>562100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>564600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>556200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>545300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>546500</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E81" s="3">
         <v>26100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>25700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>26400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>24700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>25200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>33900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>29800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>26100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>27300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>30900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>35200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>37100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>14300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>16400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>14400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>11700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>10000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5413,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5224,13 +5423,13 @@
         <v>2000</v>
       </c>
       <c r="E83" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="F83" s="3">
         <v>1900</v>
       </c>
       <c r="G83" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="H83" s="3">
         <v>2000</v>
@@ -5239,16 +5438,16 @@
         <v>2000</v>
       </c>
       <c r="J83" s="3">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="K83" s="3">
         <v>1800</v>
       </c>
       <c r="L83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M83" s="3">
         <v>1900</v>
-      </c>
-      <c r="M83" s="3">
-        <v>1000</v>
       </c>
       <c r="N83" s="3">
         <v>1000</v>
@@ -5257,22 +5456,22 @@
         <v>1000</v>
       </c>
       <c r="P83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>8400</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>1900</v>
       </c>
       <c r="R83" s="3">
         <v>1900</v>
       </c>
       <c r="S83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T83" s="3">
         <v>2000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>1100</v>
       </c>
       <c r="V83" s="3">
         <v>1100</v>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E89" s="3">
         <v>13300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>63600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>25800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>59500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>38100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>31100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>31300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>38900</v>
-      </c>
-      <c r="N89" s="3">
-        <v>49000</v>
       </c>
       <c r="O89" s="3">
         <v>49000</v>
       </c>
       <c r="P89" s="3">
+        <v>49000</v>
+      </c>
+      <c r="Q89" s="3">
         <v>34900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>33300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>24800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>16100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-20200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>30500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>15900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,67 +5937,68 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3100</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-1200</v>
       </c>
       <c r="O91" s="3">
         <v>-1200</v>
       </c>
       <c r="P91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-200</v>
       </c>
       <c r="S91" s="3">
         <v>-200</v>
       </c>
       <c r="T91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-300</v>
       </c>
       <c r="W91" s="3">
         <v>-300</v>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3">
         <v>-300</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-478700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>24900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-41800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>147400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>113500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>138900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>103300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-109600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>160500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>91600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-159900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>203000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>511100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-203200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-61900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-172300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-324600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>69000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>146300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-24700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,37 +6248,38 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E96" s="3">
         <v>7600</v>
-      </c>
-      <c r="E96" s="3">
-        <v>7200</v>
       </c>
       <c r="F96" s="3">
         <v>7200</v>
       </c>
       <c r="G96" s="3">
+        <v>7200</v>
+      </c>
+      <c r="H96" s="3">
         <v>7300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>7500</v>
-      </c>
-      <c r="I96" s="3">
-        <v>6900</v>
       </c>
       <c r="J96" s="3">
         <v>6900</v>
       </c>
       <c r="K96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="L96" s="3">
         <v>7000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>6900</v>
       </c>
       <c r="M96" s="3">
         <v>6900</v>
@@ -6057,19 +6291,19 @@
         <v>6900</v>
       </c>
       <c r="P96" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-2900</v>
       </c>
       <c r="S96" s="3">
         <v>-2900</v>
       </c>
       <c r="T96" s="3">
-        <v>-3200</v>
+        <v>-2900</v>
       </c>
       <c r="U96" s="3">
         <v>-3200</v>
@@ -6078,13 +6312,16 @@
         <v>-3200</v>
       </c>
       <c r="W96" s="3">
-        <v>-2500</v>
+        <v>-3200</v>
       </c>
       <c r="X96" s="3">
         <v>-2500</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>-2500</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,76 +6530,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>81800</v>
+      </c>
+      <c r="E100" s="3">
         <v>156400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>61800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>33500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-492300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>277600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-172500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-50900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>79000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-94900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-132300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>151700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-360400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-386500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-48400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-246100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>112400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>296200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>110800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>28800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>75400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>123600</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6396,8 +6645,8 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6423,72 +6672,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>130100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-309000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>150300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>17500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-350600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>395000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>26000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>90500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>97000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>40800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-108400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>193900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-115000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-406500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-58100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-48600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>210400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>183700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>66700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>160400</v>
       </c>
     </row>
